--- a/sampleprojects/CorporateTax/excel/states/CO_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/CO_corp.xlsx
@@ -46,7 +46,7 @@
     <t/>
   </si>
   <si>
-    <t>// Initialize Colorado filing requirement check; set result.co_has_nexus = false;</t>
+    <t>// Initialize Colorado filing requirement check; set co_result.has_nexus = false;</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold; result.co_gross_receipts &gt;= result.co_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.co_gross_receipts &gt;= result.co_economic_nexus_threshold</t>
+    <t>co_result.gross_receipts &gt;= co_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>// Physical nexus established - filing required; set result.co_has_nexus = true;</t>
+    <t>// Physical nexus established - filing required; set co_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -94,13 +94,13 @@
     <t>Economic nexus - filing required</t>
   </si>
   <si>
-    <t>// Economic nexus established per Wayfair - filing required; set result.co_has_nexus = true;</t>
+    <t>// Economic nexus established per Wayfair - filing required; set co_result.has_nexus = true;</t>
   </si>
   <si>
     <t>No nexus - no filing required; // No nexus - no filing required; set result.co_has_nexus = false; set result.co_tax_liability = 0.0;</t>
   </si>
   <si>
-    <t>set result.co_has_nexus = false; set result.co_tax_liability = 0.0;</t>
+    <t>set co_result.has_nexus = false; set co_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate CO Income Adjustments</t>
@@ -112,25 +112,25 @@
     <t>TABLE_NUMBER: 51420</t>
   </si>
   <si>
-    <t>// Initialize Colorado income adjustments; set result.co_state_additions = 0.0; set result.co_state_subtractions = 0.0;</t>
+    <t>// Initialize Colorado income adjustments; set co_result.state_additions = 0.0; set co_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>Has Colorado nexus</t>
   </si>
   <si>
-    <t>result.co_has_nexus is true</t>
+    <t>co_result.has_nexus is true</t>
   </si>
   <si>
     <t>Calculate Colorado state additions and subtractions; // Calculate Colorado state additions and subtractions; set result.co_state_additions = result.co_us_interest_income; set result.co_state_subtractions = result.co_state_tax_deduction;</t>
   </si>
   <si>
-    <t>set result.co_state_additions = result.co_us_interest_income; set result.co_state_subtractions = result.co_state_tax_deduction;</t>
+    <t>set co_result.state_additions = co_result.us_interest_income; set co_result.state_subtractions = co_result.state_tax_deduction;</t>
   </si>
   <si>
     <t>No nexus - no adjustments; // No nexus - no adjustments; set result.co_state_additions = 0.0; set result.co_state_subtractions = 0.0;</t>
   </si>
   <si>
-    <t>set result.co_state_additions = 0.0; set result.co_state_subtractions = 0.0;</t>
+    <t>set co_result.state_additions = 0.0; set co_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate CO State Tax</t>
@@ -142,25 +142,25 @@
     <t>TABLE_NUMBER: 51480</t>
   </si>
   <si>
-    <t>// Initialize Colorado tax calculation; set result.co_taxable_income = 0.0; set result.co_tax_liability = 0.0;</t>
+    <t>// Initialize Colorado tax calculation; set co_result.taxable_income = 0.0; set co_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>Has positive taxable income</t>
   </si>
   <si>
-    <t>result.co_apportioned_income &gt; 0.0</t>
+    <t>co_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Colorado corporate tax (flat rate 4.55%); // Calculate Colorado taxable income and tax; set result.co_taxable_income = (result.co_apportioned_income + result.co_state_additions - result.co_state_subtractions); set result.co_tax_liability = result.co_taxable_income * result.co_corp_tax_rate - result.co_state_credits; set result.co_refund_or_owed = result.co_estimated_payments - result.co_tax_liability;</t>
   </si>
   <si>
-    <t>if result.co_apportioned_income + result.co_state_additions - result.co_state_subtractions &gt; 0.0 then set result.co_taxable_income = result.co_apportioned_income + result.co_state_additions - result.co_state_subtractions; else set result.co_taxable_income = 0.0; endif if result.co_taxable_income * result.co_corp_tax_rate - result.co_state_credits &gt; 0.0 then set result.co_tax_liability = result.co_taxable_income * result.co_corp_tax_rate - result.co_state_credits; else set result.co_tax_liability = 0.0; endif set result.co_refund_or_owed = result.co_estimated_payments - result.co_tax_liability;</t>
+    <t>if co_result.apportioned_income + co_result.state_additions - co_result.state_subtractions &gt; 0.0 then set co_result.taxable_income = co_result.apportioned_income + co_result.state_additions - co_result.state_subtractions; else set co_result.taxable_income = 0.0; endif if co_result.taxable_income * co_result.corp_tax_rate - co_result.state_credits &gt; 0.0 then set co_result.tax_liability = co_result.taxable_income * co_result.corp_tax_rate - co_result.state_credits; else set co_result.tax_liability = 0.0; endif set co_result.refund_or_owed = co_result.estimated_payments - co_result.tax_liability;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability; // No taxable income - no tax liability; set result.co_taxable_income = 0.0; set result.co_tax_liability = 0.0; set result.co_refund_or_owed = result.co_estimated_payments;</t>
   </si>
   <si>
-    <t>set result.co_taxable_income = 0.0; set result.co_tax_liability = 0.0; set result.co_refund_or_owed = result.co_estimated_payments;</t>
+    <t>set co_result.taxable_income = 0.0; set co_result.tax_liability = 0.0; set co_result.refund_or_owed = co_result.estimated_payments;</t>
   </si>
   <si>
     <t>No nexus - no tax liability; // No nexus - no tax liability; set result.co_taxable_income = 0.0; set result.co_tax_liability = 0.0; set result.co_refund_or_owed = result.co_estimated_payments;</t>
@@ -208,13 +208,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>co_result</t>
   </si>
   <si>
     <t>(16 attributes)</t>
   </si>
   <si>
-    <t>co_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -229,7 +229,7 @@
     <t>Declared from decision-table usage; referenced by CO but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>co_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -241,7 +241,7 @@
     <t>CO uses single-sales factor apportionment (100% sales)</t>
   </si>
   <si>
-    <t>co_corp_tax_rate</t>
+    <t>corp_tax_rate</t>
   </si>
   <si>
     <t>0.0455</t>
@@ -250,7 +250,7 @@
     <t>CO corporate income tax rate: 4.55% (CO Rev. Stat. § 39-22-104, 2025)</t>
   </si>
   <si>
-    <t>co_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -259,13 +259,13 @@
     <t>CO economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>co_estimated_payments</t>
-  </si>
-  <si>
-    <t>co_gross_receipts</t>
-  </si>
-  <si>
-    <t>co_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -277,43 +277,43 @@
     <t>Whether corporation has nexus with Colorado</t>
   </si>
   <si>
-    <t>co_refund_or_owed</t>
-  </si>
-  <si>
-    <t>co_state_additions</t>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>state_additions</t>
   </si>
   <si>
     <t>CO additions to federal taxable income (U.S. interest, IRC 199A addback, etc.)</t>
   </si>
   <si>
-    <t>co_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>CO state tax credits (R&amp;D, jobs, film, renewable energy, etc.)</t>
   </si>
   <si>
-    <t>co_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>CO subtractions from federal taxable income (state taxes, CO NOL, etc.)</t>
   </si>
   <si>
-    <t>co_state_tax_deduction</t>
-  </si>
-  <si>
-    <t>co_tax_liability</t>
+    <t>state_tax_deduction</t>
+  </si>
+  <si>
+    <t>tax_liability</t>
   </si>
   <si>
     <t>CO corporate income tax liability</t>
   </si>
   <si>
-    <t>co_taxable_income</t>
+    <t>taxable_income</t>
   </si>
   <si>
     <t>CO taxable income after apportionment and modifications</t>
   </si>
   <si>
-    <t>co_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -325,7 +325,7 @@
     <t>CO economic nexus transaction count threshold: 200 transactions</t>
   </si>
   <si>
-    <t>co_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
